--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/149.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/149.xlsx
@@ -426,13 +426,13 @@
         <v>-7.633859283989217</v>
       </c>
       <c r="E2">
-        <v>-19.29933939074694</v>
+        <v>-19.03225452224855</v>
       </c>
       <c r="F2">
-        <v>-1.226395601989967</v>
+        <v>0.5096098222199426</v>
       </c>
       <c r="G2">
-        <v>-10.67165725505734</v>
+        <v>-12.08313483008993</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.290556057447457</v>
       </c>
       <c r="E3">
-        <v>-22.02156814182187</v>
+        <v>-20.12586288120491</v>
       </c>
       <c r="F3">
-        <v>-1.113591014178939</v>
+        <v>0.5395652442399782</v>
       </c>
       <c r="G3">
-        <v>-10.82523677316967</v>
+        <v>-11.65241630270305</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.063889360159238</v>
       </c>
       <c r="E4">
-        <v>-20.98972816833013</v>
+        <v>-19.68320001848112</v>
       </c>
       <c r="F4">
-        <v>-1.337779539705195</v>
+        <v>0.4118632970570036</v>
       </c>
       <c r="G4">
-        <v>-9.401937240016348</v>
+        <v>-11.18155078956143</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.991217583740063</v>
       </c>
       <c r="E5">
-        <v>-20.2973607203494</v>
+        <v>-20.34726450391392</v>
       </c>
       <c r="F5">
-        <v>-0.8405511778073885</v>
+        <v>0.7449398893138512</v>
       </c>
       <c r="G5">
-        <v>-9.314456074141107</v>
+        <v>-10.61709284347907</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.061532018863277</v>
       </c>
       <c r="E6">
-        <v>-21.93524637028765</v>
+        <v>-20.66395427669233</v>
       </c>
       <c r="F6">
-        <v>-1.278692092863506</v>
+        <v>0.6249434157117176</v>
       </c>
       <c r="G6">
-        <v>-10.02226726316498</v>
+        <v>-10.82990795292558</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.255712193429115</v>
       </c>
       <c r="E7">
-        <v>-20.69714799116856</v>
+        <v>-21.48877053244941</v>
       </c>
       <c r="F7">
-        <v>-1.09179252597427</v>
+        <v>0.7689857382823153</v>
       </c>
       <c r="G7">
-        <v>-9.378740247422675</v>
+        <v>-10.229941095389</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.552047655612911</v>
       </c>
       <c r="E8">
-        <v>-22.83794332202865</v>
+        <v>-21.22051731765704</v>
       </c>
       <c r="F8">
-        <v>-1.417202577918208</v>
+        <v>0.9400585175736637</v>
       </c>
       <c r="G8">
-        <v>-9.306391585207443</v>
+        <v>-10.29178539660813</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.928366161323454</v>
       </c>
       <c r="E9">
-        <v>-23.69623858612443</v>
+        <v>-22.14709744131449</v>
       </c>
       <c r="F9">
-        <v>-0.6742994968003333</v>
+        <v>1.073765300059532</v>
       </c>
       <c r="G9">
-        <v>-8.554722288879301</v>
+        <v>-10.16293896421969</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.341578936329794</v>
       </c>
       <c r="E10">
-        <v>-25.36036221446314</v>
+        <v>-22.37594840376612</v>
       </c>
       <c r="F10">
-        <v>-0.8036010214381137</v>
+        <v>0.956095710491862</v>
       </c>
       <c r="G10">
-        <v>-7.979200499604702</v>
+        <v>-9.313145098107556</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-8.766373433382446</v>
       </c>
       <c r="E11">
-        <v>-23.85363475720903</v>
+        <v>-22.80239480106844</v>
       </c>
       <c r="F11">
-        <v>-0.496136720908424</v>
+        <v>1.389111516426859</v>
       </c>
       <c r="G11">
-        <v>-7.890024334413354</v>
+        <v>-9.209432327453268</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.175262519707388</v>
       </c>
       <c r="E12">
-        <v>-23.70798997617434</v>
+        <v>-23.80752583486293</v>
       </c>
       <c r="F12">
-        <v>-0.5566887213182623</v>
+        <v>1.42751628595545</v>
       </c>
       <c r="G12">
-        <v>-9.011090923104453</v>
+        <v>-8.457054574379724</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.532348122023366</v>
       </c>
       <c r="E13">
-        <v>-25.91354248534412</v>
+        <v>-23.94873723984412</v>
       </c>
       <c r="F13">
-        <v>-0.5167183373983806</v>
+        <v>1.892929541013935</v>
       </c>
       <c r="G13">
-        <v>-8.368570313206083</v>
+        <v>-8.88877950761054</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.824996417218099</v>
       </c>
       <c r="E14">
-        <v>-25.70718445328859</v>
+        <v>-24.87678911755406</v>
       </c>
       <c r="F14">
-        <v>-0.04721294737006557</v>
+        <v>2.036111189853024</v>
       </c>
       <c r="G14">
-        <v>-7.765554443227836</v>
+        <v>-8.28950124354613</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.03756115456093</v>
       </c>
       <c r="E15">
-        <v>-26.75528164846786</v>
+        <v>-25.43235136576307</v>
       </c>
       <c r="F15">
-        <v>0.3498086381784871</v>
+        <v>2.174594338783434</v>
       </c>
       <c r="G15">
-        <v>-9.303749769867103</v>
+        <v>-8.508483899332301</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.15049752116822</v>
       </c>
       <c r="E16">
-        <v>-26.52037611626798</v>
+        <v>-25.74381075106263</v>
       </c>
       <c r="F16">
-        <v>0.3364628109519842</v>
+        <v>2.363829901748564</v>
       </c>
       <c r="G16">
-        <v>-7.616212423405774</v>
+        <v>-7.528847126624407</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.16794935009589</v>
       </c>
       <c r="E17">
-        <v>-27.74193197983706</v>
+        <v>-27.84986815780988</v>
       </c>
       <c r="F17">
-        <v>1.707645290560158</v>
+        <v>3.010511482092054</v>
       </c>
       <c r="G17">
-        <v>-7.547068369272555</v>
+        <v>-8.399765583822635</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.09033790335949</v>
       </c>
       <c r="E18">
-        <v>-29.77044606191397</v>
+        <v>-28.25462316461546</v>
       </c>
       <c r="F18">
-        <v>1.610313777466022</v>
+        <v>3.343342877597673</v>
       </c>
       <c r="G18">
-        <v>-7.4815460519593</v>
+        <v>-7.730234232869352</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.917212267995623</v>
       </c>
       <c r="E19">
-        <v>-30.0348410168518</v>
+        <v>-28.69742188155947</v>
       </c>
       <c r="F19">
-        <v>1.702512726132412</v>
+        <v>3.23896692811013</v>
       </c>
       <c r="G19">
-        <v>-7.517197316871711</v>
+        <v>-7.382239617417782</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.66910833199775</v>
       </c>
       <c r="E20">
-        <v>-29.7996343411304</v>
+        <v>-29.66299216642296</v>
       </c>
       <c r="F20">
-        <v>1.59599461854123</v>
+        <v>3.901821553625878</v>
       </c>
       <c r="G20">
-        <v>-7.930204425623488</v>
+        <v>-7.897648520790296</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.358315999302588</v>
       </c>
       <c r="E21">
-        <v>-31.65104433324133</v>
+        <v>-30.70255092386077</v>
       </c>
       <c r="F21">
-        <v>1.962162831805112</v>
+        <v>3.902129706299719</v>
       </c>
       <c r="G21">
-        <v>-6.634705192468191</v>
+        <v>-6.970987097801819</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.998091553109454</v>
       </c>
       <c r="E22">
-        <v>-29.53008824700884</v>
+        <v>-31.16769313155863</v>
       </c>
       <c r="F22">
-        <v>1.811419845313269</v>
+        <v>4.309008863941585</v>
       </c>
       <c r="G22">
-        <v>-6.385841552644558</v>
+        <v>-7.199864974204872</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.615642026224192</v>
       </c>
       <c r="E23">
-        <v>-31.89460151503287</v>
+        <v>-32.07115539540692</v>
       </c>
       <c r="F23">
-        <v>1.925282258297672</v>
+        <v>4.222099869509472</v>
       </c>
       <c r="G23">
-        <v>-5.868687991772849</v>
+        <v>-6.78951292297559</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.225504022047826</v>
       </c>
       <c r="E24">
-        <v>-31.83827861956247</v>
+        <v>-32.56160045162264</v>
       </c>
       <c r="F24">
-        <v>1.949763828520009</v>
+        <v>4.438698064523876</v>
       </c>
       <c r="G24">
-        <v>-6.3837459773182</v>
+        <v>-7.130667951343026</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.84370786883887</v>
       </c>
       <c r="E25">
-        <v>-31.57086543669853</v>
+        <v>-32.24088939392541</v>
       </c>
       <c r="F25">
-        <v>2.129372105529804</v>
+        <v>4.364128430923865</v>
       </c>
       <c r="G25">
-        <v>-7.774714722734999</v>
+        <v>-6.612014713342027</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.492868272845441</v>
       </c>
       <c r="E26">
-        <v>-31.27631990181762</v>
+        <v>-32.27073430187297</v>
       </c>
       <c r="F26">
-        <v>2.681692698285596</v>
+        <v>4.371944905736681</v>
       </c>
       <c r="G26">
-        <v>-6.510284959465762</v>
+        <v>-6.802758415678214</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.178963131748322</v>
       </c>
       <c r="E27">
-        <v>-33.46572840115006</v>
+        <v>-32.88362703101909</v>
       </c>
       <c r="F27">
-        <v>2.820215608851341</v>
+        <v>4.347705218795962</v>
       </c>
       <c r="G27">
-        <v>-6.058120718075486</v>
+        <v>-6.391701218249068</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-6.911063247045419</v>
       </c>
       <c r="E28">
-        <v>-33.00226172883504</v>
+        <v>-32.70205786568155</v>
       </c>
       <c r="F28">
-        <v>2.534877830017829</v>
+        <v>4.055876352994113</v>
       </c>
       <c r="G28">
-        <v>-5.691262614141149</v>
+        <v>-6.73182666695379</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.699603474726823</v>
       </c>
       <c r="E29">
-        <v>-30.87939462657131</v>
+        <v>-32.18566918187589</v>
       </c>
       <c r="F29">
-        <v>2.039606900292838</v>
+        <v>4.117271631420001</v>
       </c>
       <c r="G29">
-        <v>-6.594098040883491</v>
+        <v>-6.82112863287563</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.538689079148347</v>
       </c>
       <c r="E30">
-        <v>-33.06410936259479</v>
+        <v>-32.36606773668245</v>
       </c>
       <c r="F30">
-        <v>2.317800838644607</v>
+        <v>3.997060610660542</v>
       </c>
       <c r="G30">
-        <v>-6.094430781550212</v>
+        <v>-6.000997254795362</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.430624955362523</v>
       </c>
       <c r="E31">
-        <v>-32.8170969551354</v>
+        <v>-32.91273379770339</v>
       </c>
       <c r="F31">
-        <v>1.852935962806775</v>
+        <v>3.925146722953906</v>
       </c>
       <c r="G31">
-        <v>-6.124583230321894</v>
+        <v>-6.744496124732581</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.37612419197481</v>
       </c>
       <c r="E32">
-        <v>-31.89781673157832</v>
+        <v>-32.28640055770251</v>
       </c>
       <c r="F32">
-        <v>1.461278884558752</v>
+        <v>3.768040218073757</v>
       </c>
       <c r="G32">
-        <v>-5.616166199128322</v>
+        <v>-6.406767510998291</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.361396656262949</v>
       </c>
       <c r="E33">
-        <v>-31.91724162083422</v>
+        <v>-32.05365057913027</v>
       </c>
       <c r="F33">
-        <v>2.186307453859019</v>
+        <v>3.82881256421274</v>
       </c>
       <c r="G33">
-        <v>-7.092153064539144</v>
+        <v>-6.541314702805351</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.384648894921685</v>
       </c>
       <c r="E34">
-        <v>-31.15841428831692</v>
+        <v>-30.94926445203566</v>
       </c>
       <c r="F34">
-        <v>1.409022155320548</v>
+        <v>3.453875253622822</v>
       </c>
       <c r="G34">
-        <v>-5.78392147323981</v>
+        <v>-6.852896627870477</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.44067755783354</v>
       </c>
       <c r="E35">
-        <v>-32.01967343865072</v>
+        <v>-30.90057429950518</v>
       </c>
       <c r="F35">
-        <v>1.579932574600947</v>
+        <v>3.690372490387276</v>
       </c>
       <c r="G35">
-        <v>-6.112956594387973</v>
+        <v>-6.818122657525972</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.512197693092737</v>
       </c>
       <c r="E36">
-        <v>-31.47604145521492</v>
+        <v>-30.59221918313789</v>
       </c>
       <c r="F36">
-        <v>1.641551512225591</v>
+        <v>3.496047438099345</v>
       </c>
       <c r="G36">
-        <v>-5.9352299571122</v>
+        <v>-6.538649713646238</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.595529115487557</v>
       </c>
       <c r="E37">
-        <v>-30.8607350494227</v>
+        <v>-30.65285318586359</v>
       </c>
       <c r="F37">
-        <v>1.217659344865028</v>
+        <v>3.505071672585443</v>
       </c>
       <c r="G37">
-        <v>-6.906448012513727</v>
+        <v>-6.226183872922126</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.68093930135945</v>
       </c>
       <c r="E38">
-        <v>-29.70355370810966</v>
+        <v>-30.15052767808875</v>
       </c>
       <c r="F38">
-        <v>1.707252644411231</v>
+        <v>3.617436397305585</v>
       </c>
       <c r="G38">
-        <v>-5.572251812549889</v>
+        <v>-6.518942036050956</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.750203106713696</v>
       </c>
       <c r="E39">
-        <v>-29.76013019812449</v>
+        <v>-29.96365793392523</v>
       </c>
       <c r="F39">
-        <v>1.550111348100165</v>
+        <v>3.786984980575782</v>
       </c>
       <c r="G39">
-        <v>-6.715128275253706</v>
+        <v>-6.779078083435808</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.803671666687395</v>
       </c>
       <c r="E40">
-        <v>-30.53819675246339</v>
+        <v>-29.75927431653704</v>
       </c>
       <c r="F40">
-        <v>1.352562289880539</v>
+        <v>3.557469224282123</v>
       </c>
       <c r="G40">
-        <v>-5.483178274270259</v>
+        <v>-6.687481909455252</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.836569674800299</v>
       </c>
       <c r="E41">
-        <v>-28.52990909954174</v>
+        <v>-28.80529013242218</v>
       </c>
       <c r="F41">
-        <v>1.860871722525594</v>
+        <v>3.604712673998585</v>
       </c>
       <c r="G41">
-        <v>-6.073994783936291</v>
+        <v>-6.70784507506731</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.839578663956901</v>
       </c>
       <c r="E42">
-        <v>-29.75969320038275</v>
+        <v>-28.72432101716503</v>
       </c>
       <c r="F42">
-        <v>1.854738490275267</v>
+        <v>3.619288626818244</v>
       </c>
       <c r="G42">
-        <v>-5.66123596609996</v>
+        <v>-7.041154110506672</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.821198138206936</v>
       </c>
       <c r="E43">
-        <v>-28.18683190872063</v>
+        <v>-27.63239725053953</v>
       </c>
       <c r="F43">
-        <v>1.85647640508634</v>
+        <v>3.739070553263053</v>
       </c>
       <c r="G43">
-        <v>-6.112112405275459</v>
+        <v>-6.760694624056235</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.78288521891164</v>
       </c>
       <c r="E44">
-        <v>-28.04272228037454</v>
+        <v>-27.67364712027539</v>
       </c>
       <c r="F44">
-        <v>1.62814687091349</v>
+        <v>3.826932170208385</v>
       </c>
       <c r="G44">
-        <v>-6.982911682834274</v>
+        <v>-6.700194404326054</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.722955562405079</v>
       </c>
       <c r="E45">
-        <v>-27.206421814534</v>
+        <v>-26.80944672607361</v>
       </c>
       <c r="F45">
-        <v>1.327497549006632</v>
+        <v>3.629957998966302</v>
       </c>
       <c r="G45">
-        <v>-7.934961679563421</v>
+        <v>-6.977939243434289</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.65454863850102</v>
       </c>
       <c r="E46">
-        <v>-26.88416201872616</v>
+        <v>-26.68043050159508</v>
       </c>
       <c r="F46">
-        <v>1.601650711167545</v>
+        <v>3.678642807963635</v>
       </c>
       <c r="G46">
-        <v>-6.391277468420041</v>
+        <v>-7.062854736516594</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.581260921377558</v>
       </c>
       <c r="E47">
-        <v>-26.67491482025374</v>
+        <v>-26.5353834791294</v>
       </c>
       <c r="F47">
-        <v>1.824402019249943</v>
+        <v>3.606399230030684</v>
       </c>
       <c r="G47">
-        <v>-6.500237453754074</v>
+        <v>-6.894513495844655</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.505072136283664</v>
       </c>
       <c r="E48">
-        <v>-25.42524619004504</v>
+        <v>-25.52880333365244</v>
       </c>
       <c r="F48">
-        <v>1.771421296901692</v>
+        <v>3.821739963327638</v>
       </c>
       <c r="G48">
-        <v>-6.347382945114845</v>
+        <v>-6.843123897438548</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.439136389515684</v>
       </c>
       <c r="E49">
-        <v>-25.02865149340128</v>
+        <v>-25.177851126532</v>
       </c>
       <c r="F49">
-        <v>1.640850713402823</v>
+        <v>3.780129411950214</v>
       </c>
       <c r="G49">
-        <v>-6.957572767276692</v>
+        <v>-6.850218396529206</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.38575475713801</v>
       </c>
       <c r="E50">
-        <v>-23.84803303486154</v>
+        <v>-24.54589352181359</v>
       </c>
       <c r="F50">
-        <v>1.563067014279949</v>
+        <v>3.794725245587541</v>
       </c>
       <c r="G50">
-        <v>-7.011332716288917</v>
+        <v>-6.702760077118989</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.348242559827702</v>
       </c>
       <c r="E51">
-        <v>-26.29655628843887</v>
+        <v>-24.02759608621369</v>
       </c>
       <c r="F51">
-        <v>1.683647486901057</v>
+        <v>3.888198223319437</v>
       </c>
       <c r="G51">
-        <v>-7.164723533305509</v>
+        <v>-6.771046699957536</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.337532157542313</v>
       </c>
       <c r="E52">
-        <v>-24.54251075172986</v>
+        <v>-24.48119068519199</v>
       </c>
       <c r="F52">
-        <v>1.510351369500594</v>
+        <v>3.488030498375052</v>
       </c>
       <c r="G52">
-        <v>-7.594528350123547</v>
+        <v>-6.596120784207986</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.352225132962608</v>
       </c>
       <c r="E53">
-        <v>-24.33919132573347</v>
+        <v>-23.87093352791834</v>
       </c>
       <c r="F53">
-        <v>1.837848078932184</v>
+        <v>3.472558252025562</v>
       </c>
       <c r="G53">
-        <v>-6.419642222600517</v>
+        <v>-6.804748053547317</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.393802265212194</v>
       </c>
       <c r="E54">
-        <v>-24.16043434275469</v>
+        <v>-23.56992586062849</v>
       </c>
       <c r="F54">
-        <v>2.043778558533336</v>
+        <v>3.726529070784669</v>
       </c>
       <c r="G54">
-        <v>-7.962012147164806</v>
+        <v>-6.782252896607969</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.468161035832627</v>
       </c>
       <c r="E55">
-        <v>-23.91102410830824</v>
+        <v>-23.62618309322577</v>
       </c>
       <c r="F55">
-        <v>1.673703764597851</v>
+        <v>3.905607192656671</v>
       </c>
       <c r="G55">
-        <v>-7.198878431634169</v>
+        <v>-6.802030095659575</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.568258907743835</v>
       </c>
       <c r="E56">
-        <v>-24.58919026180092</v>
+        <v>-22.95036721774307</v>
       </c>
       <c r="F56">
-        <v>2.000618960112676</v>
+        <v>3.549056324939291</v>
       </c>
       <c r="G56">
-        <v>-6.64420314762036</v>
+        <v>-6.828137057782268</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.693603612246181</v>
       </c>
       <c r="E57">
-        <v>-21.43055699908081</v>
+        <v>-22.24482191040002</v>
       </c>
       <c r="F57">
-        <v>1.874493396097229</v>
+        <v>3.871657383020336</v>
       </c>
       <c r="G57">
-        <v>-7.565302854102861</v>
+        <v>-7.62463114071214</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.845470608460039</v>
       </c>
       <c r="E58">
-        <v>-21.63890755969971</v>
+        <v>-21.89967973543141</v>
       </c>
       <c r="F58">
-        <v>2.286382519791227</v>
+        <v>3.777332843598362</v>
       </c>
       <c r="G58">
-        <v>-7.557321128807678</v>
+        <v>-7.402814657944353</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.012445169115429</v>
       </c>
       <c r="E59">
-        <v>-22.48743943383496</v>
+        <v>-21.96714494119768</v>
       </c>
       <c r="F59">
-        <v>1.999974490273298</v>
+        <v>3.662844184857442</v>
       </c>
       <c r="G59">
-        <v>-7.23076229572289</v>
+        <v>-6.837039114737368</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.194262340113436</v>
       </c>
       <c r="E60">
-        <v>-22.11393089768231</v>
+        <v>-21.12824965975076</v>
       </c>
       <c r="F60">
-        <v>2.13846095267332</v>
+        <v>3.610903891967108</v>
       </c>
       <c r="G60">
-        <v>-7.691527334424193</v>
+        <v>-7.359459753562057</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.389769813658923</v>
       </c>
       <c r="E61">
-        <v>-22.19752652786391</v>
+        <v>-21.62879094876658</v>
       </c>
       <c r="F61">
-        <v>2.06127036461085</v>
+        <v>3.753846970994191</v>
       </c>
       <c r="G61">
-        <v>-6.990621943395237</v>
+        <v>-6.991668075785646</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.585214495503852</v>
       </c>
       <c r="E62">
-        <v>-20.37314926134177</v>
+        <v>-21.28941352120974</v>
       </c>
       <c r="F62">
-        <v>1.884349311455738</v>
+        <v>3.772937526159108</v>
       </c>
       <c r="G62">
-        <v>-8.23498649015095</v>
+        <v>-8.113085582303908</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.781970548199652</v>
       </c>
       <c r="E63">
-        <v>-21.88868007206678</v>
+        <v>-20.582283247964</v>
       </c>
       <c r="F63">
-        <v>1.541128531984207</v>
+        <v>3.880431450550789</v>
       </c>
       <c r="G63">
-        <v>-8.808015438634479</v>
+        <v>-7.59606113270823</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.976517188906892</v>
       </c>
       <c r="E64">
-        <v>-21.5332175048347</v>
+        <v>-21.6358870675366</v>
       </c>
       <c r="F64">
-        <v>1.144072155004737</v>
+        <v>3.80990756334605</v>
       </c>
       <c r="G64">
-        <v>-8.495188748446587</v>
+        <v>-8.212663481579645</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.154138467227876</v>
       </c>
       <c r="E65">
-        <v>-21.84493048467868</v>
+        <v>-20.02133211568585</v>
       </c>
       <c r="F65">
-        <v>2.285921947515271</v>
+        <v>3.760006711001408</v>
       </c>
       <c r="G65">
-        <v>-7.584484154957399</v>
+        <v>-8.074209846036245</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.316710232845129</v>
       </c>
       <c r="E66">
-        <v>-21.05002479974226</v>
+        <v>-19.50254107641912</v>
       </c>
       <c r="F66">
-        <v>1.728087741326444</v>
+        <v>3.655082382293211</v>
       </c>
       <c r="G66">
-        <v>-9.199030593368878</v>
+        <v>-7.596822558182262</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.458308028230844</v>
       </c>
       <c r="E67">
-        <v>-20.49672678853708</v>
+        <v>-20.30842378235013</v>
       </c>
       <c r="F67">
-        <v>1.558721398884863</v>
+        <v>3.531117200464265</v>
       </c>
       <c r="G67">
-        <v>-8.798775706034373</v>
+        <v>-7.930134904167164</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.564116228879584</v>
       </c>
       <c r="E68">
-        <v>-20.93052289915385</v>
+        <v>-20.59549733511838</v>
       </c>
       <c r="F68">
-        <v>1.493417883052567</v>
+        <v>3.499806569373249</v>
       </c>
       <c r="G68">
-        <v>-7.739884473116327</v>
+        <v>-8.182007829885993</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.636188211727708</v>
       </c>
       <c r="E69">
-        <v>-21.38701119302305</v>
+        <v>-19.8081677871968</v>
       </c>
       <c r="F69">
-        <v>1.494110398201307</v>
+        <v>3.305120348897698</v>
       </c>
       <c r="G69">
-        <v>-8.182083972433398</v>
+        <v>-8.109341355298991</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.665983922907296</v>
       </c>
       <c r="E70">
-        <v>-20.55114093221325</v>
+        <v>-19.39390298497511</v>
       </c>
       <c r="F70">
-        <v>1.76024165043351</v>
+        <v>3.436346999379585</v>
       </c>
       <c r="G70">
-        <v>-7.5889269070711</v>
+        <v>-8.027911866669537</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.642084429977626</v>
       </c>
       <c r="E71">
-        <v>-20.95435172938221</v>
+        <v>-20.22509080366098</v>
       </c>
       <c r="F71">
-        <v>2.142052753731858</v>
+        <v>3.271460467852343</v>
       </c>
       <c r="G71">
-        <v>-8.508616321153871</v>
+        <v>-8.211974888107477</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.56804775361095</v>
       </c>
       <c r="E72">
-        <v>-20.20579950438831</v>
+        <v>-20.36552331111285</v>
       </c>
       <c r="F72">
-        <v>1.823421232245029</v>
+        <v>3.397740108204711</v>
       </c>
       <c r="G72">
-        <v>-7.897055933138766</v>
+        <v>-8.128612040883089</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.438482438005206</v>
       </c>
       <c r="E73">
-        <v>-20.81849298067809</v>
+        <v>-20.11508511306666</v>
       </c>
       <c r="F73">
-        <v>1.492635904224324</v>
+        <v>3.281922748149701</v>
       </c>
       <c r="G73">
-        <v>-6.86037846078923</v>
+        <v>-7.877735589371579</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.251184055857038</v>
       </c>
       <c r="E74">
-        <v>-22.3860921855433</v>
+        <v>-19.2105224300345</v>
       </c>
       <c r="F74">
-        <v>1.314457389351762</v>
+        <v>3.309876834524573</v>
       </c>
       <c r="G74">
-        <v>-8.506795521107273</v>
+        <v>-7.451373739914382</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.015694990393349</v>
       </c>
       <c r="E75">
-        <v>-21.72762942245799</v>
+        <v>-20.11572362790174</v>
       </c>
       <c r="F75">
-        <v>1.513199296631419</v>
+        <v>3.153104990075156</v>
       </c>
       <c r="G75">
-        <v>-7.174972982295092</v>
+        <v>-7.787202100509131</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.733338916490797</v>
       </c>
       <c r="E76">
-        <v>-20.89983343080387</v>
+        <v>-20.40082276600264</v>
       </c>
       <c r="F76">
-        <v>1.104071949858354</v>
+        <v>3.214937646489722</v>
       </c>
       <c r="G76">
-        <v>-7.064165712550146</v>
+        <v>-7.935262939207495</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.412485713808994</v>
       </c>
       <c r="E77">
-        <v>-21.08768811806405</v>
+        <v>-20.57040053216787</v>
       </c>
       <c r="F77">
-        <v>1.116631656419601</v>
+        <v>3.08610332106712</v>
       </c>
       <c r="G77">
-        <v>-6.67132313667807</v>
+        <v>-7.2413427992664</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.068105438280349</v>
       </c>
       <c r="E78">
-        <v>-22.1249079186769</v>
+        <v>-20.89905453327455</v>
       </c>
       <c r="F78">
-        <v>0.7713913172200451</v>
+        <v>2.852487146129604</v>
       </c>
       <c r="G78">
-        <v>-6.527042940985553</v>
+        <v>-7.973135580176757</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.705453213058212</v>
       </c>
       <c r="E79">
-        <v>-21.15829155631764</v>
+        <v>-22.33841641119055</v>
       </c>
       <c r="F79">
-        <v>1.380812931785613</v>
+        <v>2.666884802593152</v>
       </c>
       <c r="G79">
-        <v>-6.505196650971902</v>
+        <v>-7.267429898115857</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.337427727003188</v>
       </c>
       <c r="E80">
-        <v>-22.59456501496041</v>
+        <v>-21.598341489539</v>
       </c>
       <c r="F80">
-        <v>0.9372652626914236</v>
+        <v>2.93665424445845</v>
       </c>
       <c r="G80">
-        <v>-7.120944879094186</v>
+        <v>-7.374559151766674</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.976822571665462</v>
       </c>
       <c r="E81">
-        <v>-22.98015551976553</v>
+        <v>-21.80711319824062</v>
       </c>
       <c r="F81">
-        <v>1.098439051519318</v>
+        <v>2.802538248475599</v>
       </c>
       <c r="G81">
-        <v>-6.246878093088111</v>
+        <v>-7.057461857833122</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.625765146981482</v>
       </c>
       <c r="E82">
-        <v>-23.03838263855615</v>
+        <v>-23.49593965229117</v>
       </c>
       <c r="F82">
-        <v>0.5913903940613237</v>
+        <v>2.639964518736974</v>
       </c>
       <c r="G82">
-        <v>-6.133783236375528</v>
+        <v>-6.642243304661112</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.296614055607416</v>
       </c>
       <c r="E83">
-        <v>-24.14198081117344</v>
+        <v>-23.03260430572237</v>
       </c>
       <c r="F83">
-        <v>0.7025597846192257</v>
+        <v>2.659573631896044</v>
       </c>
       <c r="G83">
-        <v>-5.397395418256663</v>
+        <v>-6.714721078152376</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.998865732596093</v>
       </c>
       <c r="E84">
-        <v>-24.29754295028493</v>
+        <v>-23.71964173979607</v>
       </c>
       <c r="F84">
-        <v>0.4062560781074538</v>
+        <v>2.481231100277727</v>
       </c>
       <c r="G84">
-        <v>-5.752994356811938</v>
+        <v>-6.443623814486998</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.731901626573748</v>
       </c>
       <c r="E85">
-        <v>-24.08183814787757</v>
+        <v>-25.29283813853477</v>
       </c>
       <c r="F85">
-        <v>0.8468953492504144</v>
+        <v>2.655484810395826</v>
       </c>
       <c r="G85">
-        <v>-5.874077559910782</v>
+        <v>-6.659878580748809</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.507637234522227</v>
       </c>
       <c r="E86">
-        <v>-26.1224092919999</v>
+        <v>-25.56416165870434</v>
       </c>
       <c r="F86">
-        <v>0.3631561221397955</v>
+        <v>2.493373309667962</v>
       </c>
       <c r="G86">
-        <v>-5.821876877847554</v>
+        <v>-6.056389302758447</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.333240649737232</v>
       </c>
       <c r="E87">
-        <v>-27.12017249858392</v>
+        <v>-27.36608675109645</v>
       </c>
       <c r="F87">
-        <v>0.01501815376524729</v>
+        <v>2.286811614105877</v>
       </c>
       <c r="G87">
-        <v>-5.730111866044497</v>
+        <v>-5.956374411471525</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.206004361378941</v>
       </c>
       <c r="E88">
-        <v>-27.36419384896124</v>
+        <v>-27.40130016498009</v>
       </c>
       <c r="F88">
-        <v>-0.2354826339435316</v>
+        <v>1.997370103158897</v>
       </c>
       <c r="G88">
-        <v>-5.054992314220923</v>
+        <v>-6.387847743241356</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.138320113362677</v>
       </c>
       <c r="E89">
-        <v>-28.32860484447876</v>
+        <v>-29.36148636699227</v>
       </c>
       <c r="F89">
-        <v>-0.2273356405369985</v>
+        <v>2.155323199524706</v>
       </c>
       <c r="G89">
-        <v>-5.327152263004407</v>
+        <v>-5.737941306244872</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.13567145074822</v>
       </c>
       <c r="E90">
-        <v>-30.07826908258536</v>
+        <v>-30.52440754911003</v>
       </c>
       <c r="F90">
-        <v>-0.1004148438148638</v>
+        <v>1.860760721293619</v>
       </c>
       <c r="G90">
-        <v>-6.085210912223341</v>
+        <v>-6.767630216961008</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.194080688365319</v>
       </c>
       <c r="E91">
-        <v>-32.91751586625549</v>
+        <v>-32.7467244690562</v>
       </c>
       <c r="F91">
-        <v>-0.9568812972847315</v>
+        <v>1.658806405225905</v>
       </c>
       <c r="G91">
-        <v>-5.390108907524728</v>
+        <v>-6.42035398989146</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.324249091717472</v>
       </c>
       <c r="E92">
-        <v>-34.67084590407129</v>
+        <v>-33.66183849652623</v>
       </c>
       <c r="F92">
-        <v>-0.4739928034967877</v>
+        <v>1.494819480698104</v>
       </c>
       <c r="G92">
-        <v>-5.746836742108894</v>
+        <v>-6.011617484885344</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.527552097631846</v>
       </c>
       <c r="E93">
-        <v>-34.56666835952483</v>
+        <v>-35.12377481737047</v>
       </c>
       <c r="F93">
-        <v>-0.3631961782701454</v>
+        <v>1.394156273909908</v>
       </c>
       <c r="G93">
-        <v>-5.99868649400895</v>
+        <v>-6.198547438760291</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.7942746431963</v>
       </c>
       <c r="E94">
-        <v>-38.13364997317561</v>
+        <v>-36.72753615142393</v>
       </c>
       <c r="F94">
-        <v>-1.35283346051627</v>
+        <v>1.352408213543618</v>
       </c>
       <c r="G94">
-        <v>-6.54513507235767</v>
+        <v>-5.553249281154472</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.12707119883951</v>
       </c>
       <c r="E95">
-        <v>-38.64005337179436</v>
+        <v>-38.6324047791954</v>
       </c>
       <c r="F95">
-        <v>-1.560865508218324</v>
+        <v>0.8686366801042902</v>
       </c>
       <c r="G95">
-        <v>-5.380985044018496</v>
+        <v>-5.941417366725098</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.518758315746018</v>
       </c>
       <c r="E96">
-        <v>-39.83652375359795</v>
+        <v>-41.30777740971297</v>
       </c>
       <c r="F96">
-        <v>-1.993301456971361</v>
+        <v>0.9469041457903987</v>
       </c>
       <c r="G96">
-        <v>-6.010253540123164</v>
+        <v>-6.348048364768238</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.947567970028496</v>
       </c>
       <c r="E97">
-        <v>-41.90685376466169</v>
+        <v>-42.81951788769356</v>
       </c>
       <c r="F97">
-        <v>-2.124130491099903</v>
+        <v>0.2372343365054371</v>
       </c>
       <c r="G97">
-        <v>-5.978975505868129</v>
+        <v>-6.655700672278249</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.41274697886422</v>
       </c>
       <c r="E98">
-        <v>-44.26549133766076</v>
+        <v>-44.93430845656461</v>
       </c>
       <c r="F98">
-        <v>-1.810214036869809</v>
+        <v>-0.09113381543389816</v>
       </c>
       <c r="G98">
-        <v>-6.444074048680339</v>
+        <v>-6.113751125317399</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.884203958960605</v>
       </c>
       <c r="E99">
-        <v>-45.65111381452774</v>
+        <v>-46.97518980115647</v>
       </c>
       <c r="F99">
-        <v>-2.862156144950095</v>
+        <v>-0.2868306441408646</v>
       </c>
       <c r="G99">
-        <v>-7.460712788880667</v>
+        <v>-6.879794810377055</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.354579065719224</v>
       </c>
       <c r="E100">
-        <v>-47.97121860219555</v>
+        <v>-49.18777503046016</v>
       </c>
       <c r="F100">
-        <v>-2.305671349260429</v>
+        <v>-0.3547658832118548</v>
       </c>
       <c r="G100">
-        <v>-6.396382329641598</v>
+        <v>-6.838144836947484</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.784161643494674</v>
       </c>
       <c r="E101">
-        <v>-50.67457946631752</v>
+        <v>-50.73213863519201</v>
       </c>
       <c r="F101">
-        <v>-3.199459067696026</v>
+        <v>-0.9252186100475259</v>
       </c>
       <c r="G101">
-        <v>-6.798613612663047</v>
+        <v>-6.838578518413128</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.194705907234837</v>
       </c>
       <c r="E102">
-        <v>-52.660628915506</v>
+        <v>-53.07043543506713</v>
       </c>
       <c r="F102">
-        <v>-3.288101835102198</v>
+        <v>-1.093115428716541</v>
       </c>
       <c r="G102">
-        <v>-7.216258795715342</v>
+        <v>-6.919945106677336</v>
       </c>
     </row>
   </sheetData>
